--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-condition.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-condition.xlsx
@@ -377,7 +377,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -603,7 +603,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-category</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-category|4.0.1</t>
   </si>
   <si>
     <t>&lt; 404684003 |Clinical finding|</t>
@@ -673,7 +673,7 @@
     <t>状態や診断の特定</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -718,7 +718,7 @@
     <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
@@ -987,7 +987,7 @@
     <t>状態段階を説明するコード（例：がんの段階）</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">con-1
@@ -1025,7 +1025,7 @@
     <t>状態分類を表すコード（例：臨床的または病理学的）。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage-type</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage-type|4.0.1</t>
   </si>
   <si>
     <t>./inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="stage type"]</t>
@@ -1072,7 +1072,7 @@
     <t>症状や現れ方を記述するコード。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom</t>
+    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">con-2
@@ -1091,7 +1091,7 @@
     <t>Condition.evidence.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1453,7 +1453,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="30.1328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="45.96875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.00390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
